--- a/uploads/fixed_OUTCOMES_MAPPING_PHA.B.xlsx
+++ b/uploads/fixed_OUTCOMES_MAPPING_PHA.B.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIGGA_2</t>
+          <t>BC_2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIGGA_6, NIGGA_7</t>
+          <t>BC_6, BC_7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIGGA_6, NIGGA_7</t>
+          <t>BC_6, BC_7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIGGA_2</t>
+          <t>BC_2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NIGGA_1</t>
+          <t>BC_1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIGGA_6, NIGGA_7</t>
+          <t>BC_6, BC_7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_7</t>
+          <t>BC_1, BC_7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_7</t>
+          <t>BC_1, BC_7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NIGGA_3</t>
+          <t>BC_3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NIGGA_3</t>
+          <t>BC_3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NIGGA_2</t>
+          <t>BC_2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NIGGA_6, NIGGA_7</t>
+          <t>BC_6, BC_7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NIGGA_6, NIGGA_7</t>
+          <t>BC_6, BC_7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_6</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NIGGA_1</t>
+          <t>BC_1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NIGGA_3</t>
+          <t>BC_3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_5, NIGGA_7</t>
+          <t>BC_2, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_6</t>
+          <t>BC_2, BC_6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_7</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_7</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NIGGA_5, NIGGA_6</t>
+          <t>BC_5, BC_6</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NIGGA_5, NIGGA_6</t>
+          <t>BC_5, BC_6</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NIGGA_5, NIGGA_7</t>
+          <t>BC_5, BC_7</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_7, NIGGA_6</t>
+          <t>BC_1, BC_2, BC_3, BC_7, BC_6</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_5</t>
+          <t>BC_2, BC_5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_6</t>
+          <t>BC_1, BC_3, BC_4, BC_6</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NIGGA_3</t>
+          <t>BC_3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NIGGA_7</t>
+          <t>BC_7</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3</t>
+          <t>BC_1, BC_2, BC_3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_7</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NIGGA_6</t>
+          <t>BC_6</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NIGGA_3</t>
+          <t>BC_3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NIGGA_7</t>
+          <t>BC_7</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_7</t>
+          <t>BC_2, BC_7</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3</t>
+          <t>BC_1, BC_2, BC_3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_5, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_5, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NIGGA_2, NIGGA_5, NIGGA_7</t>
+          <t>BC_2, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_2, NIGGA_3, NIGGA_4, NIGGA_6, NIGGA_7</t>
+          <t>BC_1, BC_2, BC_3, BC_4, BC_6, BC_7</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_7</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4, NIGGA_5, NIGGA_7</t>
+          <t>BC_1, BC_3, BC_4, BC_5, BC_7</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>NIGGA_1, NIGGA_3, NIGGA_4</t>
+          <t>BC_1, BC_3, BC_4</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">

--- a/uploads/fixed_OUTCOMES_MAPPING_PHA.B.xlsx
+++ b/uploads/fixed_OUTCOMES_MAPPING_PHA.B.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
